--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:17</t>
+    <t xml:space="preserve">2026-09-09 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:12</t>
+    <t xml:space="preserve">2026-09-17 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:08</t>
+    <t xml:space="preserve">2026-09-23 12:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:37</t>
+    <t xml:space="preserve">2026-10-02 14:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2023_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:54</t>
+    <t xml:space="preserve">2026-10-05 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -636,7 +636,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>263644.12</v>
+        <v>263644.13</v>
       </c>
     </row>
     <row r="10">
